--- a/public/hub/documents/master-tactical-planner-90-dias.xlsx
+++ b/public/hub/documents/master-tactical-planner-90-dias.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Dashboard" sheetId="1" r:id="Rbc7d01fb09c9455e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Master Roadmap" sheetId="2" r:id="R49f1f77e20cb43e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Instagram Calendar" sheetId="3" r:id="R57a2d116ab9e4857"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Content Library" sheetId="4" r:id="Rb7a33a5b25ea4f73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_GEO Actions" sheetId="5" r:id="R1f298bd5a5b44e9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_AI Visibility" sheetId="6" r:id="Rbde5fb2da1244649"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Creators" sheetId="7" r:id="R2c470a87fedd4234"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Dashboard" sheetId="1" r:id="R892c194a65a84ec9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Master Roadmap" sheetId="2" r:id="Ra791fc7c863942c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Instagram Calendar" sheetId="3" r:id="R64c91d9b91de41cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Content Library" sheetId="4" r:id="Rd559b781a98e4305"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_GEO Actions" sheetId="5" r:id="Rb890d81bed2448c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_AI Visibility" sheetId="6" r:id="R2d473f194f7d4fce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Creators" sheetId="7" r:id="R3fb261d07e68400f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -53,8 +53,14 @@
       <x:color rgb="FFC46A3A"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FFC46A3A"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -86,6 +92,11 @@
         <x:fgColor rgb="FFF3E4DB"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3EFE6"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -94,7 +105,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="52">
+  <x:cellXfs count="57">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -207,10 +218,186 @@
     <x:xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:dxfs count="15">
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF233426"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE7F0E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF233426"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE7F0E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF36566E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF3EFE6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFC46A3A"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF7EBDD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF747B74"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF1F0ED"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF233426"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE7F0E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF233426"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE7F0E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF36566E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF3EFE6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFC46A3A"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF7EBDD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF747B74"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF1F0ED"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF233426"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE7F0E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF233426"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE7F0E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF36566E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF3EFE6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFC46A3A"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF7EBDD"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF747B74"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF1F0ED"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
 </x:styleSheet>
 </file>
 
@@ -584,6 +771,22 @@
       <x:c r="K2" s="9"/>
       <x:c r="L2" s="9"/>
     </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="56" t="str">
+        <x:v>STATUS ATUAL · 25/08/2026 · FOUNDATION EM EXECUÇÃO · GATE G1 EM VALIDAÇÃO · HUB E FORMULÁRIO OPERACIONAIS</x:v>
+      </x:c>
+      <x:c r="B3" s="56"/>
+      <x:c r="C3" s="56"/>
+      <x:c r="D3" s="56"/>
+      <x:c r="E3" s="56"/>
+      <x:c r="F3" s="56"/>
+      <x:c r="G3" s="56"/>
+      <x:c r="H3" s="56"/>
+      <x:c r="I3" s="56"/>
+      <x:c r="J3" s="56"/>
+      <x:c r="K3" s="56"/>
+      <x:c r="L3" s="56"/>
+    </x:row>
     <x:row r="4" ht="28" customHeight="1">
       <x:c r="A4" s="16" t="str">
         <x:v>VISÃO EXECUTIVA</x:v>
@@ -652,7 +855,7 @@
         <x:v>Entity audit, técnico, baseline</x:v>
       </x:c>
       <x:c r="F7" s="32" t="str">
-        <x:v>Base validada</x:v>
+        <x:v>Base em validação</x:v>
       </x:c>
       <x:c r="H7" s="32" t="str">
         <x:v>G0</x:v>
@@ -667,7 +870,7 @@
         <x:v>Proprietários</x:v>
       </x:c>
       <x:c r="L7" s="32" t="str">
-        <x:v>Pendente</x:v>
+        <x:v>Aprovado</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -687,7 +890,7 @@
         <x:v>Listings + conteúdo trilíngue</x:v>
       </x:c>
       <x:c r="F8" s="32" t="str">
-        <x:v>Operação rodando</x:v>
+        <x:v>Gate G1 consolidado</x:v>
       </x:c>
       <x:c r="H8" s="32" t="str">
         <x:v>G1</x:v>
@@ -702,7 +905,7 @@
         <x:v>Proprietários</x:v>
       </x:c>
       <x:c r="L8" s="32" t="str">
-        <x:v>Pendente</x:v>
+        <x:v>Em validação</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -880,7 +1083,25 @@
     <x:mergeCell ref="A2:L2"/>
     <x:mergeCell ref="A4:L4"/>
     <x:mergeCell ref="A13:L13"/>
+    <x:mergeCell ref="A3:L3"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="L7:L11">
+    <x:cfRule type="expression" dxfId="0" priority="1">
+      <x:formula>L7="Concluído"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="1" priority="2">
+      <x:formula>L7="Aprovado"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="2" priority="3">
+      <x:formula>L7="Em andamento"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="3" priority="4">
+      <x:formula>L7="Em validação"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="4" priority="5">
+      <x:formula>L7="Pendente"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="L7:L11">
       <x:formula1>"Pendente,Aprovado,Revisar"</x:formula1>
@@ -906,7 +1127,7 @@
     <x:col min="10" max="10" width="29" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="23" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="10" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="32" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -1007,7 +1228,7 @@
         <x:v>Proprietários</x:v>
       </x:c>
       <x:c r="H5" s="32" t="str">
-        <x:v>Pendente</x:v>
+        <x:v>Concluído</x:v>
       </x:c>
       <x:c r="I5" s="32" t="str">
         <x:v>—</x:v>
@@ -1022,7 +1243,7 @@
         <x:v>G0</x:v>
       </x:c>
       <x:c r="M5" s="32" t="str">
-        <x:v>Sem silêncio absoluto / luxo ostensivo</x:v>
+        <x:v>Estratégia aprovada; assinatura “Reservado por natureza.” e guardrails fechados.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1048,7 +1269,7 @@
         <x:v>Quinta</x:v>
       </x:c>
       <x:c r="H6" s="32" t="str">
-        <x:v>Pendente</x:v>
+        <x:v>Em validação</x:v>
       </x:c>
       <x:c r="I6" s="32" t="str">
         <x:v>—</x:v>
@@ -1063,7 +1284,7 @@
         <x:v>G1</x:v>
       </x:c>
       <x:c r="M6" s="32" t="str">
-        <x:v>Base de todos os canais</x:v>
+        <x:v>Bangalôs 01–04 mapeados; Bangalô 05 pendente na validação Gate G1.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1089,7 +1310,7 @@
         <x:v>Proprietários</x:v>
       </x:c>
       <x:c r="H7" s="32" t="str">
-        <x:v>Pendente</x:v>
+        <x:v>Em validação</x:v>
       </x:c>
       <x:c r="I7" s="32" t="str">
         <x:v>—</x:v>
@@ -1103,7 +1324,9 @@
       <x:c r="L7" s="32" t="str">
         <x:v>G1</x:v>
       </x:c>
-      <x:c r="M7" s="32" t="str"/>
+      <x:c r="M7" s="32" t="str">
+        <x:v>Airbnb é a preferência inicial; Booking, Decolar e TripAdvisor já mapeados. Decisão final pendente.</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="32" t="str">
@@ -1167,7 +1390,7 @@
         <x:v>Estratégia</x:v>
       </x:c>
       <x:c r="H9" s="32" t="str">
-        <x:v>Pendente</x:v>
+        <x:v>Concluído</x:v>
       </x:c>
       <x:c r="I9" s="32" t="str">
         <x:v>Posicionamento aprovado</x:v>
@@ -1181,7 +1404,9 @@
       <x:c r="L9" s="32" t="str">
         <x:v>G1</x:v>
       </x:c>
-      <x:c r="M9" s="32" t="str"/>
+      <x:c r="M9" s="32" t="str">
+        <x:v>Pilares definidos: Quinta; Between River &amp; Sea; Living Caraíva; Your Stay; Trust &amp; Plan.</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="32" t="str">
@@ -1206,7 +1431,7 @@
         <x:v>Estratégia</x:v>
       </x:c>
       <x:c r="H10" s="32" t="str">
-        <x:v>Pendente</x:v>
+        <x:v>Concluído</x:v>
       </x:c>
       <x:c r="I10" s="32" t="str">
         <x:v>Posicionamento aprovado</x:v>
@@ -1220,7 +1445,9 @@
       <x:c r="L10" s="32" t="str">
         <x:v>G1</x:v>
       </x:c>
-      <x:c r="M10" s="32" t="str"/>
+      <x:c r="M10" s="32" t="str">
+        <x:v>PT principal; EN/ES localizados; direção verbal/editorial definida.</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="32" t="str">
@@ -1245,7 +1472,7 @@
         <x:v>Conteúdo</x:v>
       </x:c>
       <x:c r="H11" s="32" t="str">
-        <x:v>Pendente</x:v>
+        <x:v>Concluído</x:v>
       </x:c>
       <x:c r="I11" s="32" t="str">
         <x:v>Acesso aos assets</x:v>
@@ -1259,7 +1486,9 @@
       <x:c r="L11" s="32" t="str">
         <x:v>G1</x:v>
       </x:c>
-      <x:c r="M11" s="32" t="str"/>
+      <x:c r="M11" s="32" t="str">
+        <x:v>Biblioteca do Hub organizada; acervo Airbnb dos Bangalôs 01–04 recebido.</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="32" t="str">
@@ -1284,7 +1513,7 @@
         <x:v>Conteúdo</x:v>
       </x:c>
       <x:c r="H12" s="32" t="str">
-        <x:v>Pendente</x:v>
+        <x:v>Em andamento</x:v>
       </x:c>
       <x:c r="I12" s="32" t="str">
         <x:v>Biblioteca organizada</x:v>
@@ -1298,7 +1527,9 @@
       <x:c r="L12" s="32" t="str">
         <x:v>G1</x:v>
       </x:c>
-      <x:c r="M12" s="32" t="str"/>
+      <x:c r="M12" s="32" t="str">
+        <x:v>Gaps finais dependem principalmente da confirmação do Bangalô 05 e de novos assets operacionais.</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="32" t="str">
@@ -1323,7 +1554,7 @@
         <x:v>Social</x:v>
       </x:c>
       <x:c r="H13" s="32" t="str">
-        <x:v>Pendente</x:v>
+        <x:v>Em andamento</x:v>
       </x:c>
       <x:c r="I13" s="32" t="str">
         <x:v>Guia verbal</x:v>
@@ -1337,7 +1568,9 @@
       <x:c r="L13" s="32" t="str">
         <x:v>G1</x:v>
       </x:c>
-      <x:c r="M13" s="32" t="str"/>
+      <x:c r="M13" s="32" t="str">
+        <x:v>Instagram será implantado do zero; nome já reservado e estrutura em preparação.</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="32" t="str">
@@ -1401,7 +1634,7 @@
         <x:v>GEO</x:v>
       </x:c>
       <x:c r="H15" s="32" t="str">
-        <x:v>Pendente</x:v>
+        <x:v>Em validação</x:v>
       </x:c>
       <x:c r="I15" s="32" t="str">
         <x:v>Dados oficiais</x:v>
@@ -1415,7 +1648,9 @@
       <x:c r="L15" s="32" t="str">
         <x:v>G1</x:v>
       </x:c>
-      <x:c r="M15" s="32" t="str"/>
+      <x:c r="M15" s="32" t="str">
+        <x:v>Source of Truth pré-preenchida; formulário Gate G1 publicado e envio automático testado.</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="32" t="str">
@@ -1440,7 +1675,7 @@
         <x:v>GEO</x:v>
       </x:c>
       <x:c r="H16" s="32" t="str">
-        <x:v>Pendente</x:v>
+        <x:v>Em andamento</x:v>
       </x:c>
       <x:c r="I16" s="32" t="str">
         <x:v>Source of Truth</x:v>
@@ -1454,7 +1689,9 @@
       <x:c r="L16" s="32" t="str">
         <x:v>G1</x:v>
       </x:c>
-      <x:c r="M16" s="32" t="str"/>
+      <x:c r="M16" s="32" t="str">
+        <x:v>Site, Airbnb, Booking, Decolar e TripAdvisor auditados; divergências consolidadas para validação.</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="32" t="str">
@@ -2904,6 +3141,23 @@
     <x:mergeCell ref="A1:M1"/>
     <x:mergeCell ref="A2:M2"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="H5:H53">
+    <x:cfRule type="expression" dxfId="5" priority="1">
+      <x:formula>H5="Concluído"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="6" priority="2">
+      <x:formula>H5="Aprovado"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="7" priority="3">
+      <x:formula>H5="Em andamento"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="8" priority="4">
+      <x:formula>H5="Em validação"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="9" priority="5">
+      <x:formula>H5="Pendente"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="D5:D53">
       <x:formula1>"P0,P1,P2"</x:formula1>
@@ -2914,7 +3168,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R117eb3d14e424b23"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf894e9a0508340c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4624,7 +4878,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R624af12e4c7842f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c94f5a86e7b4413"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4634,7 +4888,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
@@ -4725,79 +4979,93 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="32" t="str">
-        <x:v>Q001</x:v>
-      </x:c>
-      <x:c r="B5" s="32" t="str"/>
+        <x:v>AB01</x:v>
+      </x:c>
+      <x:c r="B5" s="32" t="str">
+        <x:v>Pacote Airbnb · Bangalô 01</x:v>
+      </x:c>
       <x:c r="C5" s="32" t="str">
         <x:v>Foto</x:v>
       </x:c>
       <x:c r="D5" s="32" t="str">
-        <x:v>Quinta</x:v>
+        <x:v>Your Stay</x:v>
       </x:c>
       <x:c r="E5" s="32" t="str">
-        <x:v>Arquitetura</x:v>
+        <x:v>Bangalô 01</x:v>
       </x:c>
       <x:c r="F5" s="32" t="str">
-        <x:v>Vertical</x:v>
+        <x:v>Mista</x:v>
       </x:c>
       <x:c r="G5" s="32" t="str">
-        <x:v>Hero</x:v>
+        <x:v>A / Editorial</x:v>
       </x:c>
       <x:c r="H5" s="32" t="str">
-        <x:v>Instagram / Site</x:v>
+        <x:v>Site / OTAs / Instagram</x:v>
       </x:c>
       <x:c r="I5" s="32" t="str">
         <x:v>Todos</x:v>
       </x:c>
       <x:c r="J5" s="32" t="str">
-        <x:v>Próprio</x:v>
+        <x:v>Recebido da Quinta</x:v>
       </x:c>
       <x:c r="K5" s="32" t="str">
         <x:v>Disponível</x:v>
       </x:c>
-      <x:c r="L5" s="32" t="str"/>
-      <x:c r="M5" s="32" t="str"/>
+      <x:c r="L5" s="32" t="str">
+        <x:v>25/08/2026</x:v>
+      </x:c>
+      <x:c r="M5" s="32" t="str">
+        <x:v>19 imagens recebidas</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="32" t="str">
-        <x:v>Q002</x:v>
-      </x:c>
-      <x:c r="B6" s="32" t="str"/>
+        <x:v>AB02</x:v>
+      </x:c>
+      <x:c r="B6" s="32" t="str">
+        <x:v>Pacote Airbnb · Bangalô 02</x:v>
+      </x:c>
       <x:c r="C6" s="32" t="str">
-        <x:v>Vídeo</x:v>
+        <x:v>Foto</x:v>
       </x:c>
       <x:c r="D6" s="32" t="str">
-        <x:v>Between River &amp; Sea</x:v>
+        <x:v>Your Stay</x:v>
       </x:c>
       <x:c r="E6" s="32" t="str">
-        <x:v>Rio</x:v>
+        <x:v>Bangalô 02</x:v>
       </x:c>
       <x:c r="F6" s="32" t="str">
-        <x:v>Vertical</x:v>
+        <x:v>Mista</x:v>
       </x:c>
       <x:c r="G6" s="32" t="str">
-        <x:v>Hero</x:v>
+        <x:v>A / Editorial</x:v>
       </x:c>
       <x:c r="H6" s="32" t="str">
-        <x:v>Reel / Stories</x:v>
+        <x:v>Site / OTAs / Instagram</x:v>
       </x:c>
       <x:c r="I6" s="32" t="str">
         <x:v>Todos</x:v>
       </x:c>
       <x:c r="J6" s="32" t="str">
-        <x:v>Próprio</x:v>
+        <x:v>Recebido da Quinta</x:v>
       </x:c>
       <x:c r="K6" s="32" t="str">
         <x:v>Disponível</x:v>
       </x:c>
-      <x:c r="L6" s="32" t="str"/>
-      <x:c r="M6" s="32" t="str"/>
+      <x:c r="L6" s="32" t="str">
+        <x:v>25/08/2026</x:v>
+      </x:c>
+      <x:c r="M6" s="32" t="str">
+        <x:v>16 imagens recebidas</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="32" t="str">
-        <x:v>Q003</x:v>
-      </x:c>
-      <x:c r="B7" s="32" t="str"/>
+        <x:v>AB03</x:v>
+      </x:c>
+      <x:c r="B7" s="32" t="str">
+        <x:v>Pacote Airbnb · Bangalô 03</x:v>
+      </x:c>
       <x:c r="C7" s="32" t="str">
         <x:v>Foto</x:v>
       </x:c>
@@ -4805,98 +5073,104 @@
         <x:v>Your Stay</x:v>
       </x:c>
       <x:c r="E7" s="32" t="str">
-        <x:v>Bangalô</x:v>
+        <x:v>Bangalô 03</x:v>
       </x:c>
       <x:c r="F7" s="32" t="str">
-        <x:v>Horizontal</x:v>
+        <x:v>Mista</x:v>
       </x:c>
       <x:c r="G7" s="32" t="str">
-        <x:v>A</x:v>
+        <x:v>A / Editorial</x:v>
       </x:c>
       <x:c r="H7" s="32" t="str">
-        <x:v>Site / OTAs</x:v>
+        <x:v>Site / OTAs / Instagram</x:v>
       </x:c>
       <x:c r="I7" s="32" t="str">
         <x:v>Todos</x:v>
       </x:c>
       <x:c r="J7" s="32" t="str">
-        <x:v>Próprio</x:v>
+        <x:v>Recebido da Quinta</x:v>
       </x:c>
       <x:c r="K7" s="32" t="str">
         <x:v>Disponível</x:v>
       </x:c>
-      <x:c r="L7" s="32" t="str"/>
-      <x:c r="M7" s="32" t="str"/>
+      <x:c r="L7" s="32" t="str">
+        <x:v>25/08/2026</x:v>
+      </x:c>
+      <x:c r="M7" s="32" t="str">
+        <x:v>10 imagens recebidas</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="32" t="str">
-        <x:v>Q004</x:v>
-      </x:c>
-      <x:c r="B8" s="32" t="str"/>
+        <x:v>AB04</x:v>
+      </x:c>
+      <x:c r="B8" s="32" t="str">
+        <x:v>Pacote Airbnb · Bangalô 04</x:v>
+      </x:c>
       <x:c r="C8" s="32" t="str">
-        <x:v>Vídeo</x:v>
+        <x:v>Foto</x:v>
       </x:c>
       <x:c r="D8" s="32" t="str">
-        <x:v>Living Caraíva</x:v>
+        <x:v>Your Stay</x:v>
       </x:c>
       <x:c r="E8" s="32" t="str">
-        <x:v>Chegada</x:v>
+        <x:v>Bangalô 04</x:v>
       </x:c>
       <x:c r="F8" s="32" t="str">
-        <x:v>Vertical</x:v>
+        <x:v>Mista</x:v>
       </x:c>
       <x:c r="G8" s="32" t="str">
-        <x:v>A</x:v>
+        <x:v>A / Editorial</x:v>
       </x:c>
       <x:c r="H8" s="32" t="str">
-        <x:v>Reel / GEO</x:v>
+        <x:v>Site / OTAs / Instagram</x:v>
       </x:c>
       <x:c r="I8" s="32" t="str">
         <x:v>Todos</x:v>
       </x:c>
       <x:c r="J8" s="32" t="str">
-        <x:v>Próprio</x:v>
+        <x:v>Recebido da Quinta</x:v>
       </x:c>
       <x:c r="K8" s="32" t="str">
         <x:v>Disponível</x:v>
       </x:c>
-      <x:c r="L8" s="32" t="str"/>
-      <x:c r="M8" s="32" t="str"/>
+      <x:c r="L8" s="32" t="str">
+        <x:v>25/08/2026</x:v>
+      </x:c>
+      <x:c r="M8" s="32" t="str">
+        <x:v>9 imagens recebidas</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="32" t="str">
-        <x:v>Q005</x:v>
-      </x:c>
-      <x:c r="B9" s="32" t="str"/>
+        <x:v>PEND05</x:v>
+      </x:c>
+      <x:c r="B9" s="32"/>
       <x:c r="C9" s="32" t="str">
         <x:v>Foto</x:v>
       </x:c>
       <x:c r="D9" s="32" t="str">
-        <x:v>Trust &amp; Plan</x:v>
+        <x:v>Your Stay</x:v>
       </x:c>
       <x:c r="E9" s="32" t="str">
-        <x:v>Localização</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="str">
-        <x:v>Horizontal</x:v>
-      </x:c>
-      <x:c r="G9" s="32" t="str">
-        <x:v>A</x:v>
-      </x:c>
+        <x:v>Bangalô 05</x:v>
+      </x:c>
+      <x:c r="F9" s="32"/>
+      <x:c r="G9" s="32"/>
       <x:c r="H9" s="32" t="str">
-        <x:v>Google / Site</x:v>
+        <x:v>Site / OTAs / Instagram</x:v>
       </x:c>
       <x:c r="I9" s="32" t="str">
         <x:v>Todos</x:v>
       </x:c>
-      <x:c r="J9" s="32" t="str">
-        <x:v>Próprio</x:v>
-      </x:c>
+      <x:c r="J9" s="32"/>
       <x:c r="K9" s="32" t="str">
-        <x:v>Disponível</x:v>
-      </x:c>
-      <x:c r="L9" s="32" t="str"/>
-      <x:c r="M9" s="32" t="str"/>
+        <x:v>Pendente</x:v>
+      </x:c>
+      <x:c r="L9" s="32"/>
+      <x:c r="M9" s="32" t="str">
+        <x:v>Aguardar confirmação se entra no projeto + acervo correspondente</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="32"/>
@@ -6290,7 +6564,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53c2dd852ea64b0f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcca3e33e90244ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6311,7 +6585,7 @@
     <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="28" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="30" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -6415,7 +6689,7 @@
         <x:v>PT/EN/ES</x:v>
       </x:c>
       <x:c r="G5" s="32" t="str">
-        <x:v>Pendente</x:v>
+        <x:v>Em validação</x:v>
       </x:c>
       <x:c r="H5" s="32" t="str">
         <x:v>GEO</x:v>
@@ -6429,9 +6703,15 @@
       <x:c r="K5" s="32" t="str">
         <x:v>100% fatos críticos</x:v>
       </x:c>
-      <x:c r="L5" s="32" t="str"/>
-      <x:c r="M5" s="32" t="str"/>
-      <x:c r="N5" s="32" t="str"/>
+      <x:c r="L5" s="32" t="str">
+        <x:v>25/08/2026</x:v>
+      </x:c>
+      <x:c r="M5" s="32" t="str">
+        <x:v>Aguardar devolutiva Gate G1 e consolidar Source of Truth.</x:v>
+      </x:c>
+      <x:c r="N5" s="32" t="str">
+        <x:v>Formulário online publicado e testado.</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="32" t="str">
@@ -6453,7 +6733,7 @@
         <x:v>Todos</x:v>
       </x:c>
       <x:c r="G6" s="32" t="str">
-        <x:v>Pendente</x:v>
+        <x:v>Em andamento</x:v>
       </x:c>
       <x:c r="H6" s="32" t="str">
         <x:v>GEO</x:v>
@@ -6467,9 +6747,15 @@
       <x:c r="K6" s="32" t="str">
         <x:v>0 divergências críticas</x:v>
       </x:c>
-      <x:c r="L6" s="32" t="str"/>
-      <x:c r="M6" s="32" t="str"/>
-      <x:c r="N6" s="32" t="str"/>
+      <x:c r="L6" s="32" t="str">
+        <x:v>25/08/2026</x:v>
+      </x:c>
+      <x:c r="M6" s="32" t="str">
+        <x:v>Fechar divergências após validação da proprietária.</x:v>
+      </x:c>
+      <x:c r="N6" s="32" t="str">
+        <x:v>Site + Airbnb + Booking + Decolar + TripAdvisor já mapeados.</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="32" t="str">
@@ -6505,9 +6791,15 @@
       <x:c r="K7" s="32" t="str">
         <x:v>0 bloqueios críticos</x:v>
       </x:c>
-      <x:c r="L7" s="32" t="str"/>
-      <x:c r="M7" s="32" t="str"/>
-      <x:c r="N7" s="32" t="str"/>
+      <x:c r="L7" s="32" t="str">
+        <x:v>25/08/2026</x:v>
+      </x:c>
+      <x:c r="M7" s="32" t="str">
+        <x:v>Executar auditoria técnica completa após fechamento factual.</x:v>
+      </x:c>
+      <x:c r="N7" s="32" t="str">
+        <x:v>Limpeza técnica do código tratada separadamente; auditoria GEO técnica ainda não concluída.</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="32" t="str">
@@ -6605,7 +6897,7 @@
         <x:v>PT/EN/ES</x:v>
       </x:c>
       <x:c r="G10" s="32" t="str">
-        <x:v>Pendente</x:v>
+        <x:v>Em validação</x:v>
       </x:c>
       <x:c r="H10" s="32" t="str">
         <x:v>GEO/Operação</x:v>
@@ -6619,9 +6911,15 @@
       <x:c r="K10" s="32" t="str">
         <x:v>0 divergências críticas</x:v>
       </x:c>
-      <x:c r="L10" s="32" t="str"/>
-      <x:c r="M10" s="32" t="str"/>
-      <x:c r="N10" s="32" t="str"/>
+      <x:c r="L10" s="32" t="str">
+        <x:v>25/08/2026</x:v>
+      </x:c>
+      <x:c r="M10" s="32" t="str">
+        <x:v>Definir papel final de Airbnb/Booking e padronizar inventário/políticas.</x:v>
+      </x:c>
+      <x:c r="N10" s="32" t="str">
+        <x:v>Conflitos de horários, Wi-Fi, capacidade e inventário identificados.</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="32" t="str">
@@ -6643,7 +6941,7 @@
         <x:v>PT/EN/ES</x:v>
       </x:c>
       <x:c r="G11" s="32" t="str">
-        <x:v>Pendente</x:v>
+        <x:v>Em andamento</x:v>
       </x:c>
       <x:c r="H11" s="32" t="str">
         <x:v>GEO</x:v>
@@ -6657,9 +6955,15 @@
       <x:c r="K11" s="32" t="str">
         <x:v>Campos completos</x:v>
       </x:c>
-      <x:c r="L11" s="32" t="str"/>
-      <x:c r="M11" s="32" t="str"/>
-      <x:c r="N11" s="32" t="str"/>
+      <x:c r="L11" s="32" t="str">
+        <x:v>25/08/2026</x:v>
+      </x:c>
+      <x:c r="M11" s="32" t="str">
+        <x:v>Confirmar propriedade/gestão da ficha e reivindicar se necessário.</x:v>
+      </x:c>
+      <x:c r="N11" s="32" t="str">
+        <x:v>Página pública identificada; gestão ainda não confirmada.</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="32" t="str">
@@ -7046,6 +7350,23 @@
     <x:mergeCell ref="A1:N1"/>
     <x:mergeCell ref="A2:N2"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="G5:G21">
+    <x:cfRule type="expression" dxfId="10" priority="1">
+      <x:formula>G5="Concluído"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="11" priority="2">
+      <x:formula>G5="Aprovado"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="12" priority="3">
+      <x:formula>G5="Em andamento"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="13" priority="4">
+      <x:formula>G5="Em validação"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="14" priority="5">
+      <x:formula>G5="Pendente"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="C5:C100">
       <x:formula1>"P0,P1,P2"</x:formula1>
@@ -7056,7 +7377,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35058f2a84324d06"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb03873e7c04546c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8898,7 +9219,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f4b8f99c9a64bd0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79670139c4b94859"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10566,7 +10887,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd77ffaab311c48ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51fae39dd8ca49ad"/>
   </x:tableParts>
 </x:worksheet>
 </file>